--- a/artfynd/A 65467-2021 artfynd.xlsx
+++ b/artfynd/A 65467-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65467-2021 artfynd.xlsx
+++ b/artfynd/A 65467-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1140,6 +1140,117 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120288006</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>967</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Varglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Letharia vulpina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Idre, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>380016</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6851283</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65467-2021 artfynd.xlsx
+++ b/artfynd/A 65467-2021 artfynd.xlsx
@@ -1145,7 +1145,7 @@
         <v>120288006</v>
       </c>
       <c r="B6" t="n">
-        <v>78625</v>
+        <v>78641</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
